--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.56375102472736</v>
+        <v>7.891609541518196</v>
       </c>
       <c r="D2" t="n">
-        <v>6.324854911520061</v>
+        <v>1.02778892312201</v>
       </c>
       <c r="E2" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F2" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.99490365499908</v>
+        <v>7.799171843937351</v>
       </c>
       <c r="D3" t="n">
-        <v>17.24942318494685</v>
+        <v>2.803031267553862</v>
       </c>
       <c r="E3" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F3" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.45256208207682</v>
+        <v>6.736041338337484</v>
       </c>
       <c r="D4" t="n">
-        <v>10.16162632633664</v>
+        <v>1.651264278029704</v>
       </c>
       <c r="E4" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F4" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.40262257321199</v>
+        <v>10.14042616814695</v>
       </c>
       <c r="D5" t="n">
-        <v>24.06868349857455</v>
+        <v>3.911161068518365</v>
       </c>
       <c r="E5" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F5" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.63592944751559</v>
+        <v>6.440838535221283</v>
       </c>
       <c r="D6" t="n">
-        <v>12.52774698197742</v>
+        <v>2.035758884571331</v>
       </c>
       <c r="E6" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F6" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.17432001975428</v>
+        <v>8.315827003210071</v>
       </c>
       <c r="D7" t="n">
-        <v>12.44766823322523</v>
+        <v>2.0227460878991</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F7" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.32437034040731</v>
+        <v>3.627710180316189</v>
       </c>
       <c r="D8" t="n">
-        <v>23.50995061030065</v>
+        <v>3.820366974173855</v>
       </c>
       <c r="E8" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F8" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73241463247388</v>
+        <v>4.181517377777006</v>
       </c>
       <c r="D9" t="n">
-        <v>25.21546965205163</v>
+        <v>4.097513818458391</v>
       </c>
       <c r="E9" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F9" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.619839844755127</v>
+        <v>1.563223974772708</v>
       </c>
       <c r="D10" t="n">
-        <v>8.439616604266229</v>
+        <v>1.371437698193262</v>
       </c>
       <c r="E10" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F10" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.10786794399082</v>
+        <v>4.567528540898508</v>
       </c>
       <c r="D11" t="n">
-        <v>28.19242361326759</v>
+        <v>4.581268837155982</v>
       </c>
       <c r="E11" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F11" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.3529612293882</v>
+        <v>8.669856199775582</v>
       </c>
       <c r="D12" t="n">
-        <v>52.72259695787739</v>
+        <v>8.567422005655075</v>
       </c>
       <c r="E12" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F12" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.646604336767</v>
+        <v>7.580073204724638</v>
       </c>
       <c r="D13" t="n">
-        <v>45.71544740718021</v>
+        <v>7.428760203666785</v>
       </c>
       <c r="E13" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F13" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.11018582318938</v>
+        <v>2.130405196268275</v>
       </c>
       <c r="D14" t="n">
-        <v>12.84892435076256</v>
+        <v>2.087950206998916</v>
       </c>
       <c r="E14" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F14" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.980632211334989</v>
+        <v>1.459352734341936</v>
       </c>
       <c r="D15" t="n">
-        <v>9.387366813193099</v>
+        <v>1.525447107143879</v>
       </c>
       <c r="E15" t="n">
-        <v>16.88073445889974</v>
+        <v>2.743119349571208</v>
       </c>
       <c r="F15" t="n">
-        <v>13.49959432069318</v>
+        <v>2.193684077112642</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
